--- a/data/quotas/quota_2026_소프트웨어_동적항목_검증쿼터_1791808832505.xlsx
+++ b/data/quotas/quota_2026_소프트웨어_동적항목_검증쿼터_1791808832505.xlsx
@@ -397,17 +397,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.234375" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" customWidth="1"/>
-    <col min="9" max="9" width="12.6328125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="35.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -424,18 +426,24 @@
         <v>대표자이름</v>
       </c>
       <c r="E1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="F1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="G1" t="str">
         <v>사업장주소</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>업종</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>개업일</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>종업원수</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>기업규모</v>
       </c>
     </row>
@@ -453,24 +461,30 @@
         <v>대표자</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>경기도 부천시 송내대로265번길 59</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>소프트웨어개발</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>1990.01.01</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>변경추이</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>중견기업</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
   </ignoredErrors>
 </worksheet>
 </file>